--- a/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/2026-02-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/2026-02-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L8"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אליה אבוקרט - אמא יקרה קאבר</v>
+        <v>נגה ון-דר ולדה - מלכת הדור קאבר</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-15</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409575&amp;sid=a8a5a1e57229330c535f7e1a7942dafa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409582&amp;sid=d09027a3b24c8cd942795a30f95f3436</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-15</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>אליה אבוקרט - אמא יקרה קאבר</v>
+        <v>נגה ון-דר ולדה - מלכת הדור קאבר</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>אופק המלאך - אין מילים איתך קאבר</v>
+        <v>נאור בן דוד - כמו בימים קאבר</v>
       </c>
       <c r="B3" t="str">
         <v>2026-02-15</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409574&amp;sid=a8a5a1e57229330c535f7e1a7942dafa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409581&amp;sid=d09027a3b24c8cd942795a30f95f3436</v>
       </c>
       <c r="D3" t="str">
         <v>2026-02-15</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>אופק המלאך - אין מילים איתך קאבר</v>
+        <v>נאור בן דוד - כמו בימים קאבר</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>אופיר נגר - Aramam Cover</v>
+        <v>ליאן אמסלם - יכולה לבד קאבר</v>
       </c>
       <c r="B4" t="str">
         <v>2026-02-15</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409573&amp;sid=a8a5a1e57229330c535f7e1a7942dafa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409580&amp;sid=d09027a3b24c8cd942795a30f95f3436</v>
       </c>
       <c r="D4" t="str">
         <v>2026-02-15</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>אופיר נגר - Aramam Cover</v>
+        <v>ליאן אמסלם - יכולה לבד קאבר</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>אבישי עוזיאל - אין לי אותך קאבר</v>
+        <v>הדר מעוז - גולה סאנגם קאבר</v>
       </c>
       <c r="B5" t="str">
         <v>2026-02-15</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409572&amp;sid=a8a5a1e57229330c535f7e1a7942dafa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409579&amp;sid=d09027a3b24c8cd942795a30f95f3436</v>
       </c>
       <c r="D5" t="str">
         <v>2026-02-15</v>
@@ -583,12 +583,126 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>אבישי עוזיאל - אין לי אותך קאבר</v>
+        <v>הדר מעוז - גולה סאנגם קאבר</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>דניאל חן - התמונות שבאלבום קאבר</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-02-15</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409578&amp;sid=d09027a3b24c8cd942795a30f95f3436</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-02-15</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>דניאל חן - התמונות שבאלבום קאבר</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>דניאל בן משיח - ממעמקים קאבר</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-02-15</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409577&amp;sid=d09027a3b24c8cd942795a30f95f3436</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-02-15</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>דניאל בן משיח - ממעמקים קאבר</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>בן ישכרוב - מזל קאבר</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-02-15</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409576&amp;sid=d09027a3b24c8cd942795a30f95f3436</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-02-15</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>בן ישכרוב - מזל קאבר</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L8"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/2026-02-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/2026-02-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:L7"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>נגה ון-דר ולדה - מלכת הדור קאבר</v>
+        <v>תהל עזרא - רציתי לדבר איתך קאבר</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-15</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409582&amp;sid=d09027a3b24c8cd942795a30f95f3436</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409588&amp;sid=1be5e63e81c8e2b5e975cab900ebe0ae</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-15</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>נגה ון-דר ולדה - מלכת הדור קאבר</v>
+        <v>תהל עזרא - רציתי לדבר איתך קאבר</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>נאור בן דוד - כמו בימים קאבר</v>
+        <v>תאי חבאני - הגולה קאבר</v>
       </c>
       <c r="B3" t="str">
         <v>2026-02-15</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409581&amp;sid=d09027a3b24c8cd942795a30f95f3436</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409587&amp;sid=1be5e63e81c8e2b5e975cab900ebe0ae</v>
       </c>
       <c r="D3" t="str">
         <v>2026-02-15</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>נאור בן דוד - כמו בימים קאבר</v>
+        <v>תאי חבאני - הגולה קאבר</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>ליאן אמסלם - יכולה לבד קאבר</v>
+        <v>שרון זריהן - רק איתך קאבר</v>
       </c>
       <c r="B4" t="str">
         <v>2026-02-15</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409580&amp;sid=d09027a3b24c8cd942795a30f95f3436</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409586&amp;sid=1be5e63e81c8e2b5e975cab900ebe0ae</v>
       </c>
       <c r="D4" t="str">
         <v>2026-02-15</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>ליאן אמסלם - יכולה לבד קאבר</v>
+        <v>שרון זריהן - רק איתך קאבר</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>הדר מעוז - גולה סאנגם קאבר</v>
+        <v>שילת ויצמן - הנך יפה קאבר</v>
       </c>
       <c r="B5" t="str">
         <v>2026-02-15</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409579&amp;sid=d09027a3b24c8cd942795a30f95f3436</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409585&amp;sid=1be5e63e81c8e2b5e975cab900ebe0ae</v>
       </c>
       <c r="D5" t="str">
         <v>2026-02-15</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>הדר מעוז - גולה סאנגם קאבר</v>
+        <v>שילת ויצמן - הנך יפה קאבר</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>דניאל חן - התמונות שבאלבום קאבר</v>
+        <v>שי חזן - חי איך שבא לי קאבר</v>
       </c>
       <c r="B6" t="str">
         <v>2026-02-15</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409578&amp;sid=d09027a3b24c8cd942795a30f95f3436</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409584&amp;sid=1be5e63e81c8e2b5e975cab900ebe0ae</v>
       </c>
       <c r="D6" t="str">
         <v>2026-02-15</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>דניאל חן - התמונות שבאלבום קאבר</v>
+        <v>שי חזן - חי איך שבא לי קאבר</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>דניאל בן משיח - ממעמקים קאבר</v>
+        <v>צוריאל - הפרח בגני קאבר</v>
       </c>
       <c r="B7" t="str">
         <v>2026-02-15</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409577&amp;sid=d09027a3b24c8cd942795a30f95f3436</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409583&amp;sid=1be5e63e81c8e2b5e975cab900ebe0ae</v>
       </c>
       <c r="D7" t="str">
         <v>2026-02-15</v>
@@ -659,50 +659,12 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>דניאל בן משיח - ממעמקים קאבר</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>בן ישכרוב - מזל קאבר</v>
-      </c>
-      <c r="B8" t="str">
-        <v>2026-02-15</v>
-      </c>
-      <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409576&amp;sid=d09027a3b24c8cd942795a30f95f3436</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2026-02-15</v>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v>בן ישכרוב - מזל קאבר</v>
+        <v>צוריאל - הפרח בגני קאבר</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L7"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/2026-02-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/2026-02-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>תהל עזרא - רציתי לדבר איתך קאבר</v>
+        <v>יובל קונסטנטיני - כמה מתוק קאבר</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409588&amp;sid=1be5e63e81c8e2b5e975cab900ebe0ae</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409596&amp;sid=846b7ed9141fdd03f79af5d3710d71af</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>תהל עזרא - רציתי לדבר איתך קאבר</v>
+        <v>יובל קונסטנטיני - כמה מתוק קאבר</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>תאי חבאני - הגולה קאבר</v>
+        <v>יהל עמר - עד סוף העולם קאבר</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409587&amp;sid=1be5e63e81c8e2b5e975cab900ebe0ae</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409595&amp;sid=846b7ed9141fdd03f79af5d3710d71af</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,21 +507,21 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>תאי חבאני - הגולה קאבר</v>
+        <v>יהל עמר - עד סוף העולם קאבר</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>שרון זריהן - רק איתך קאבר</v>
+        <v>יהל עמר - הנך יפה קאבר</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409586&amp;sid=1be5e63e81c8e2b5e975cab900ebe0ae</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409594&amp;sid=846b7ed9141fdd03f79af5d3710d71af</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -545,21 +545,21 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>שרון זריהן - רק איתך קאבר</v>
+        <v>יהל עמר - הנך יפה קאבר</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>שילת ויצמן - הנך יפה קאבר</v>
+        <v>חנוך שובל - Aktar Cover</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409585&amp;sid=1be5e63e81c8e2b5e975cab900ebe0ae</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409593&amp;sid=846b7ed9141fdd03f79af5d3710d71af</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -583,21 +583,21 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>שילת ויצמן - הנך יפה קאבר</v>
+        <v>חנוך שובל - Aktar Cover</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>שי חזן - חי איך שבא לי קאבר</v>
+        <v>חגית ביטון חג'בי - Never Enough Cover</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409584&amp;sid=1be5e63e81c8e2b5e975cab900ebe0ae</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409592&amp;sid=846b7ed9141fdd03f79af5d3710d71af</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -621,21 +621,21 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>שי חזן - חי איך שבא לי קאבר</v>
+        <v>חגית ביטון חג'בי - Never Enough Cover</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>צוריאל - הפרח בגני קאבר</v>
+        <v>הודיה לוי - יכולה לבד קאבר</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409583&amp;sid=1be5e63e81c8e2b5e975cab900ebe0ae</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409591&amp;sid=846b7ed9141fdd03f79af5d3710d71af</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -659,12 +659,88 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>צוריאל - הפרח בגני קאבר</v>
+        <v>הודיה לוי - יכולה לבד קאבר</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>אלרואי &amp; אביה - מגנט &amp; הייתי חוזרת קאבר</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-02-16</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409590&amp;sid=846b7ed9141fdd03f79af5d3710d71af</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-02-16</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>אלרואי &amp; אביה - מגנט &amp; הייתי חוזרת קאבר</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>אוריה בן שושן - אלוקיי תן שלום קאבר</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-02-16</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409589&amp;sid=846b7ed9141fdd03f79af5d3710d71af</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-02-16</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>אוריה בן שושן - אלוקיי תן שלום קאבר</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L9"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/2026-02-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/2026-02-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L7"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>יובל קונסטנטיני - כמה מתוק קאבר</v>
+        <v>צביקי רנד &amp; יהודה רושגולד &amp; איציק עקשטיין - מיין הארץ קאבר</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-16</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409596&amp;sid=846b7ed9141fdd03f79af5d3710d71af</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409602&amp;sid=d67bf896a4ea73f11a2df696159cf3c7</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-16</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>יובל קונסטנטיני - כמה מתוק קאבר</v>
+        <v>צביקי רנד &amp; יהודה רושגולד &amp; איציק עקשטיין - מיין הארץ קאבר</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>יהל עמר - עד סוף העולם קאבר</v>
+        <v>שירה אורן - קצת משונה שלא נשארת קאבר</v>
       </c>
       <c r="B3" t="str">
         <v>2026-02-16</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409595&amp;sid=846b7ed9141fdd03f79af5d3710d71af</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409601&amp;sid=d67bf896a4ea73f11a2df696159cf3c7</v>
       </c>
       <c r="D3" t="str">
         <v>2026-02-16</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>יהל עמר - עד סוף העולם קאבר</v>
+        <v>שירה אורן - קצת משונה שלא נשארת קאבר</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>יהל עמר - הנך יפה קאבר</v>
+        <v>שי שלום - שרק תחייך קאבר</v>
       </c>
       <c r="B4" t="str">
         <v>2026-02-16</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409594&amp;sid=846b7ed9141fdd03f79af5d3710d71af</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409600&amp;sid=d67bf896a4ea73f11a2df696159cf3c7</v>
       </c>
       <c r="D4" t="str">
         <v>2026-02-16</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>יהל עמר - הנך יפה קאבר</v>
+        <v>שי שלום - שרק תחייך קאבר</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>חנוך שובל - Aktar Cover</v>
+        <v>עידו עמדור - תצאי לי מהראש קאבר</v>
       </c>
       <c r="B5" t="str">
         <v>2026-02-16</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409593&amp;sid=846b7ed9141fdd03f79af5d3710d71af</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409599&amp;sid=d67bf896a4ea73f11a2df696159cf3c7</v>
       </c>
       <c r="D5" t="str">
         <v>2026-02-16</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>חנוך שובל - Aktar Cover</v>
+        <v>עידו עמדור - תצאי לי מהראש קאבר</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>חגית ביטון חג'בי - Never Enough Cover</v>
+        <v>מתן טולדנו - עינייך מספרות קאבר</v>
       </c>
       <c r="B6" t="str">
         <v>2026-02-16</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409592&amp;sid=846b7ed9141fdd03f79af5d3710d71af</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409598&amp;sid=d67bf896a4ea73f11a2df696159cf3c7</v>
       </c>
       <c r="D6" t="str">
         <v>2026-02-16</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>חגית ביטון חג'בי - Never Enough Cover</v>
+        <v>מתן טולדנו - עינייך מספרות קאבר</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>הודיה לוי - יכולה לבד קאבר</v>
+        <v>ליעד - יום אהבה ראשון קאבר</v>
       </c>
       <c r="B7" t="str">
         <v>2026-02-16</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409591&amp;sid=846b7ed9141fdd03f79af5d3710d71af</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409597&amp;sid=d67bf896a4ea73f11a2df696159cf3c7</v>
       </c>
       <c r="D7" t="str">
         <v>2026-02-16</v>
@@ -659,88 +659,12 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>הודיה לוי - יכולה לבד קאבר</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>אלרואי &amp; אביה - מגנט &amp; הייתי חוזרת קאבר</v>
-      </c>
-      <c r="B8" t="str">
-        <v>2026-02-16</v>
-      </c>
-      <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409590&amp;sid=846b7ed9141fdd03f79af5d3710d71af</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2026-02-16</v>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v>אלרואי &amp; אביה - מגנט &amp; הייתי חוזרת קאבר</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>אוריה בן שושן - אלוקיי תן שלום קאבר</v>
-      </c>
-      <c r="B9" t="str">
-        <v>2026-02-16</v>
-      </c>
-      <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409589&amp;sid=846b7ed9141fdd03f79af5d3710d71af</v>
-      </c>
-      <c r="D9" t="str">
-        <v>2026-02-16</v>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v>אוריה בן שושן - אלוקיי תן שלום קאבר</v>
+        <v>ליעד - יום אהבה ראשון קאבר</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L7"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/2026-02-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/2026-02-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>צביקי רנד &amp; יהודה רושגולד &amp; איציק עקשטיין - מיין הארץ קאבר</v>
+        <v>שמוליק טליאס &amp; טהר טליאס - כינורי קאבר</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-16</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409602&amp;sid=d67bf896a4ea73f11a2df696159cf3c7</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409603&amp;sid=aaf75d33e307b5a16fb4b3cf00589b10</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-16</v>
@@ -469,202 +469,12 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>צביקי רנד &amp; יהודה רושגולד &amp; איציק עקשטיין - מיין הארץ קאבר</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>שירה אורן - קצת משונה שלא נשארת קאבר</v>
-      </c>
-      <c r="B3" t="str">
-        <v>2026-02-16</v>
-      </c>
-      <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409601&amp;sid=d67bf896a4ea73f11a2df696159cf3c7</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2026-02-16</v>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v>שירה אורן - קצת משונה שלא נשארת קאבר</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>שי שלום - שרק תחייך קאבר</v>
-      </c>
-      <c r="B4" t="str">
-        <v>2026-02-16</v>
-      </c>
-      <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409600&amp;sid=d67bf896a4ea73f11a2df696159cf3c7</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2026-02-16</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
-        <v>שי שלום - שרק תחייך קאבר</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>עידו עמדור - תצאי לי מהראש קאבר</v>
-      </c>
-      <c r="B5" t="str">
-        <v>2026-02-16</v>
-      </c>
-      <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409599&amp;sid=d67bf896a4ea73f11a2df696159cf3c7</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2026-02-16</v>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str">
-        <v>עידו עמדור - תצאי לי מהראש קאבר</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>מתן טולדנו - עינייך מספרות קאבר</v>
-      </c>
-      <c r="B6" t="str">
-        <v>2026-02-16</v>
-      </c>
-      <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409598&amp;sid=d67bf896a4ea73f11a2df696159cf3c7</v>
-      </c>
-      <c r="D6" t="str">
-        <v>2026-02-16</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
-        <v>מתן טולדנו - עינייך מספרות קאבר</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>ליעד - יום אהבה ראשון קאבר</v>
-      </c>
-      <c r="B7" t="str">
-        <v>2026-02-16</v>
-      </c>
-      <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409597&amp;sid=d67bf896a4ea73f11a2df696159cf3c7</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2026-02-16</v>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v>ליעד - יום אהבה ראשון קאבר</v>
+        <v>שמוליק טליאס &amp; טהר טליאס - כינורי קאבר</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/2026-02-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/2026-02-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L12"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שמוליק טליאס &amp; טהר טליאס - כינורי קאבר</v>
+        <v>תאי חבאני - נשבעתי לך ילדה קאבר</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-20</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409603&amp;sid=aaf75d33e307b5a16fb4b3cf00589b10</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409676&amp;sid=1d2db5b1333d25f65c24eb3f2c1667e1</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,12 +469,392 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שמוליק טליאס &amp; טהר טליאס - כינורי קאבר</v>
+        <v>תאי חבאני - נשבעתי לך ילדה קאבר</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>שלמה דעוס - היום קאבר</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-02-20</v>
+      </c>
+      <c r="C3" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409675&amp;sid=1d2db5b1333d25f65c24eb3f2c1667e1</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-02-20</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>שלמה דעוס - היום קאבר</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>נתנאל סורילוב - מאשאפ חשבונות שמיים &amp; ביחד איתי</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-02-20</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409674&amp;sid=1d2db5b1333d25f65c24eb3f2c1667e1</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-02-20</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>נתנאל סורילוב - מאשאפ חשבונות שמיים &amp; ביחד איתי</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>מאיר שטרית - תמאלי מעאק קאבר</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-02-20</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409673&amp;sid=1d2db5b1333d25f65c24eb3f2c1667e1</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-02-20</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>מאיר שטרית - תמאלי מעאק קאבר</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>זוהר אשירוב &amp; בתאל אדרי - תגידי קאבר</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-02-20</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409672&amp;sid=1d2db5b1333d25f65c24eb3f2c1667e1</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-02-20</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>זוהר אשירוב &amp; בתאל אדרי - תגידי קאבר</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>הודיה שמואל - רוח ים קאבר</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-02-20</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409671&amp;sid=1d2db5b1333d25f65c24eb3f2c1667e1</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-02-20</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>הודיה שמואל - רוח ים קאבר</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>אלון מיכאל - חבקי אותי קאבר</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-02-20</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409670&amp;sid=1d2db5b1333d25f65c24eb3f2c1667e1</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-02-20</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>אלון מיכאל - חבקי אותי קאבר</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>אחיה קובי &amp; שלומי אמסלם - לכה דודי קאבר</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-02-20</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409669&amp;sid=1d2db5b1333d25f65c24eb3f2c1667e1</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-02-20</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>אחיה קובי &amp; שלומי אמסלם - לכה דודי קאבר</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>אושר פלמן - בואי אמא קאבר</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-02-20</v>
+      </c>
+      <c r="C10" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409668&amp;sid=1d2db5b1333d25f65c24eb3f2c1667e1</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-02-20</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>אושר פלמן - בואי אמא קאבר</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>אבנר הררי &amp; איתי הררי - בין הטוב והרע קאבר</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2026-02-20</v>
+      </c>
+      <c r="C11" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409667&amp;sid=1d2db5b1333d25f65c24eb3f2c1667e1</v>
+      </c>
+      <c r="D11" t="str">
+        <v>2026-02-20</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v>אבנר הררי &amp; איתי הררי - בין הטוב והרע קאבר</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>אבירם ברמי - תחזרי קאבר</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2026-02-20</v>
+      </c>
+      <c r="C12" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409666&amp;sid=1d2db5b1333d25f65c24eb3f2c1667e1</v>
+      </c>
+      <c r="D12" t="str">
+        <v>2026-02-20</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
+        <v>אבירם ברמי - תחזרי קאבר</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L12"/>
   </ignoredErrors>
 </worksheet>
 </file>